--- a/questionnaire_templates/044_diversity_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/044_diversity_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'black_or_african_american'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Black or African American'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'american_indian_or_alaskan_native'}</t>
+          <t>american_indian_or_alaskan_native</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'American Indian or Alaskan Native'}</t>
+          <t>American Indian or Alaskan Native</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'native_hawaiian_or_other_pacific_islander'}</t>
+          <t>native_hawaiian_or_other_pacific_islander</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Native Hawaiian or Other Pacific Islander'}</t>
+          <t>Native Hawaiian or Other Pacific Islander</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_disclose'}</t>
+          <t>prefer_not_to_disclose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer not to disclose'}</t>
+          <t>Prefer not to disclose</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_answer'}</t>
+          <t>prefer_not_to_answer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer not to answer'}</t>
+          <t>Prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
